--- a/supplementary/Table S1 - Basic read statistics.xlsx
+++ b/supplementary/Table S1 - Basic read statistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Shared drives\CSMS_CBP_MassLab\Liel Uziahu\GitHub\S_Pistillata_Bet-Hedging\supplementary\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6000846-583B-4A2B-8ABF-613945E63411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EEC61C6-F0DC-47A0-8982-E9EA32C6CA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6585" yWindow="6765" windowWidth="26430" windowHeight="10065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7275" yWindow="7455" windowWidth="26430" windowHeight="10065" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
   <si>
     <t>Sample ID</t>
   </si>
@@ -82,13 +82,87 @@
   </si>
   <si>
     <t>pl_119</t>
+  </si>
+  <si>
+    <r>
+      <t>Supplementary Table 1.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Summary of RNA-seq sequencing and read mapping statistics for </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Stylophora pistillata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> high-fluorescent (HF) and non-fluorescent (NF) larval morphotypes (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>N = 10</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> libraries total; 5 HF and 5 NF samples). The table details sequencing depth at each processing stage, including raw reads, quality-trimmed reads, non-rRNA filtered reads, host-mapped reads (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>Stylophora pistillata</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> reference genome), and final gene-level read counts used for differential expression analysis.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -103,6 +177,26 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -125,7 +219,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -138,6 +232,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -419,10 +516,36 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A3:G13"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="7" max="7" width="9" customWidth="1"/>
+    <col min="8" max="8" width="29.140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="3" spans="1:7" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+    </row>
+    <row r="2" spans="1:8" ht="69" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5"/>
+      <c r="B2" s="5"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="5"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="G2" s="5"/>
+      <c r="H2" s="5"/>
+    </row>
+    <row r="3" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -445,7 +568,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -468,7 +591,7 @@
         <v>1242687</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -491,7 +614,7 @@
         <v>519147</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>10</v>
       </c>
@@ -514,7 +637,7 @@
         <v>728081</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>12</v>
       </c>
@@ -537,7 +660,7 @@
         <v>870034</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
@@ -560,7 +683,7 @@
         <v>542705</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>14</v>
       </c>
@@ -583,7 +706,7 @@
         <v>1175141</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>15</v>
       </c>
@@ -606,7 +729,7 @@
         <v>341437</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>16</v>
       </c>
@@ -629,7 +752,7 @@
         <v>507402</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>17</v>
       </c>
@@ -652,7 +775,7 @@
         <v>631905</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>18</v>
       </c>
@@ -676,6 +799,9 @@
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>